--- a/assets/constructions/examples/ctd_mic_corn902.xlsx
+++ b/assets/constructions/examples/ctd_mic_corn902.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,11 +579,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MT190L-080NC50R05SO12/AX14-088+23A-IK*</t>
+          <t>MT190L-080NC50R07SO09-131+18A-IK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -593,7 +613,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MT190L-NC..SO12/AX14+23A-IK</t>
+          <t>MT190L..NC50..SO09..+18A-IK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -605,34 +625,34 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>10500</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>SO.T120408... + AXGT1405..R</t>
+          <t>BO..12T3.. + SO..09T308..</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -643,7 +663,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SKIF_SO1204H + SKIF AX1405RH</t>
+          <t>SKIF_BO12T3H + SKIF_SO09T3H</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -653,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -669,21 +689,27 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT190L-050SK50R03SO12/AX14-053+23A</t>
+          <t>12393041200</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MT190L-SK..SO12/AX14+23A</t>
+          <t>M390</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -691,49 +717,49 @@
         <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>97.5</v>
+        <v>50</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>255</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="I3" t="n">
+        <v>82</v>
+      </c>
       <c r="J3" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>76</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>SO.T120408... + AXGT1405..R</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>DIN_2080:SK50</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SKIF_SO1204H + SKIF AX1405RH</t>
+          <t>WIDIA_CAP_D50+WIDIA_SD1204H</t>
         </is>
       </c>
       <c r="V3" t="n">
@@ -746,24 +772,40 @@
         <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>105</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>WID_CAP_D50_SD1204_H</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>WID_123969_2938</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT190L-063H100AR05SO09-072+18A-IK</t>
+          <t>MT190L-050SK50R04SO09-058+18A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -773,40 +815,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MT190L..H.A..SO09..+18A-IK</t>
+          <t>MT190L..SK50..SO09..+18A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>236</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="P4" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -816,7 +860,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>DIN_2080:SK50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -834,10 +878,10 @@
         <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
@@ -847,11 +891,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT190L-080H125AR05SO12-137+41A-H194-IK*</t>
+          <t>MT190L-050NC50R04SD08/BD12-081+18A-IK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -861,55 +911,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT190L-H.A..SO12+21A-IK</t>
+          <t>MT190L..NC50..SD08/BD12..+18A-IK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>97.5</v>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>245</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>10500</v>
+        <v>14500</v>
       </c>
       <c r="P5" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>178</v>
+        <v>99</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>SO.T120408...</t>
+          <t>BDMT1204.. + SD.T08T308.R</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK125A</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SKIF_SO1204H</t>
+          <t>SKIF_BD1204H + SKIF_SD08T3H</t>
         </is>
       </c>
       <c r="V5" t="n">
@@ -919,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
@@ -935,71 +987,77 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT190L-050SK50R04SD08/BD12-056+18A</t>
+          <t>12393041800</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MT190L..SK50..SD08/BD12..+18A</t>
+          <t>M390</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" t="n">
         <v>50</v>
-      </c>
-      <c r="F6" t="n">
-        <v>97.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>236</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>262</v>
+      </c>
+      <c r="I6" t="n">
+        <v>137</v>
+      </c>
       <c r="J6" t="n">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>15000</v>
+        <v>10500</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>74</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>BDMT1204.. + SD.T08T308.R</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>DIN_2080:SK50</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SKIF_BD1204H + SKIF_SD08T3H</t>
+          <t>WIDIA_CAP_D80+WIDIA_SD1204H</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -1009,22 +1067,38 @@
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>WID_CAP_D80_SD1204_H</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>WID_123969_2938</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
